--- a/data/trans_orig/IQ17A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ17A-Provincia-trans_orig.xlsx
@@ -1215,7 +1215,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12208</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21361</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -2402,12 +2402,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1214</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2528,12 +2528,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13847</t>
+          <t>13866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>17948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20545</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,9%</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,5%</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>680</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4523,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>18149</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>27835</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>35498</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5502,12 +5502,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>29511</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>67372</t>
+          <t>67038</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4152</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -8432,12 +8432,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -8543,12 +8543,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>21108</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>32169</t>
+          <t>31458</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>42508</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51604</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,43%</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -9361,12 +9361,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>17256</t>
+          <t>16176</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>15349</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9487,47 +9487,47 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
+          <t>9,67%</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>20384</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>27760</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
           <t>9,52%</t>
-        </is>
-      </c>
-      <c r="Q82" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
-        <is>
-          <t>20384</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>14235</t>
-        </is>
-      </c>
-      <c r="T82" s="2" t="inlineStr">
-        <is>
-          <t>28200</t>
-        </is>
-      </c>
-      <c r="U82" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="V82" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="W82" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -9548,12 +9548,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>112530</t>
+          <t>113352</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>123541</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>137939</t>
+          <t>137779</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>150775</t>
+          <t>150836</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9598,12 +9598,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>255165</t>
+          <t>256012</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>271096</t>
+          <t>271506</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -10567,12 +10567,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10637,12 +10637,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10652,12 +10652,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -10678,12 +10678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7478</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,16%</t>
         </is>
       </c>
     </row>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14506</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21501</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29555</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10874,12 +10874,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11657,12 +11657,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -11683,12 +11683,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>15797</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11768,12 +11768,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -11794,12 +11794,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19500</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26191</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11809,12 +11809,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11829,12 +11829,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16411</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24541</t>
+          <t>24115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11864,12 +11864,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>38025</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48634</t>
+          <t>48768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12506,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12693,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12763,7 +12763,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -12799,12 +12799,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12814,12 +12814,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16287</t>
+          <t>15915</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -12869,12 +12869,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>30745</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>37296</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12884,12 +12884,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -13693,12 +13693,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6911</t>
+          <t>6719</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13708,12 +13708,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13728,12 +13728,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7442</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13743,12 +13743,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13763,12 +13763,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3329</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13778,12 +13778,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,43%</t>
         </is>
       </c>
     </row>
@@ -13804,12 +13804,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11701</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13819,12 +13819,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13839,12 +13839,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13874,12 +13874,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>32114</t>
+          <t>32363</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2948</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -14733,12 +14733,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2952</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -14748,12 +14748,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -14768,12 +14768,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>10883</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -14783,12 +14783,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>8774</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>20622</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -15778,7 +15778,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>11779</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -15829,7 +15829,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -15884,12 +15884,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>26095</t>
+          <t>26330</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>31153</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -15899,12 +15899,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -16561,7 +16561,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -16576,7 +16576,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -16602,7 +16602,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -16672,7 +16672,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -16687,7 +16687,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -16743,12 +16743,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -16758,12 +16758,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -16778,12 +16778,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>9090</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -16793,12 +16793,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -16819,12 +16819,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -16834,12 +16834,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -16854,12 +16854,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>23900</t>
+          <t>23988</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -16869,12 +16869,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -16889,12 +16889,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>50458</t>
+          <t>51010</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>59180</t>
+          <t>59425</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -16904,12 +16904,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -17692,7 +17692,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -17713,12 +17713,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -17728,12 +17728,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -17748,12 +17748,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -17783,12 +17783,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -17798,12 +17798,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -17824,12 +17824,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>23734</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -17839,12 +17839,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -17859,12 +17859,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>15222</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>21452</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -17874,12 +17874,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -17894,12 +17894,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>36744</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>44500</t>
+          <t>44538</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -17909,12 +17909,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -18279,7 +18279,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -18349,7 +18349,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -18536,7 +18536,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -18586,7 +18586,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -18607,12 +18607,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -18622,12 +18622,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -18642,12 +18642,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>9281</t>
+          <t>9366</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -18657,12 +18657,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -18677,12 +18677,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>16465</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -18692,12 +18692,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -18718,12 +18718,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -18733,12 +18733,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -18753,12 +18753,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17894</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>32879</t>
+          <t>32392</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -18768,12 +18768,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -18788,12 +18788,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>50277</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -18803,12 +18803,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -18829,12 +18829,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>131835</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>145991</t>
+          <t>145161</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -18844,12 +18844,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -18864,12 +18864,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>129908</t>
+          <t>129320</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>146002</t>
+          <t>146589</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -18879,12 +18879,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -18899,12 +18899,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>265711</t>
+          <t>265382</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>287091</t>
+          <t>287705</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -18914,12 +18914,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -19888,7 +19888,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -19903,7 +19903,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -19959,12 +19959,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -19994,12 +19994,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>7088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -20009,12 +20009,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -20029,12 +20029,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -20044,12 +20044,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -20070,12 +20070,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13770</t>
+          <t>13825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -20085,12 +20085,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -20105,12 +20105,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16120</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -20120,12 +20120,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -20140,12 +20140,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28496</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -20155,12 +20155,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -20525,7 +20525,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -20964,12 +20964,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>552</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -20979,12 +20979,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -20999,12 +20999,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -21014,12 +21014,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -21034,12 +21034,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10786</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -21049,12 +21049,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -21075,12 +21075,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22107</t>
+          <t>21886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26779</t>
+          <t>26828</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -21090,12 +21090,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -21110,12 +21110,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>19384</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>25905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -21125,12 +21125,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -21145,12 +21145,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43784</t>
+          <t>43946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>51506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -21160,12 +21160,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -22009,7 +22009,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>4228</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -22059,7 +22059,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -22115,7 +22115,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13570</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -22661,7 +22661,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2865</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -22868,7 +22868,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -22883,7 +22883,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -22938,7 +22938,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -22953,7 +22953,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -22974,12 +22974,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -22989,12 +22989,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6354</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -23044,12 +23044,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -23059,12 +23059,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -23085,12 +23085,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14358</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -23100,12 +23100,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18729</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -23135,12 +23135,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -23155,12 +23155,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>36035</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>44098</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -23170,12 +23170,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -23984,7 +23984,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -24054,7 +24054,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -24069,7 +24069,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -24090,7 +24090,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6714</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -24105,7 +24105,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
@@ -24175,7 +24175,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -25059,7 +25059,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -25180,7 +25180,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -25807,7 +25807,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -25842,7 +25842,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -25857,7 +25857,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -25989,12 +25989,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>559</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -26004,12 +26004,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -26029,7 +26029,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -26044,7 +26044,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -26059,12 +26059,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -26074,12 +26074,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -26100,12 +26100,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -26115,12 +26115,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -26135,7 +26135,7 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -26170,12 +26170,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>17637</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>23391</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -26777,7 +26777,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -26792,7 +26792,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -26847,7 +26847,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -26994,12 +26994,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>5630</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -27009,12 +27009,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -27064,12 +27064,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -27079,12 +27079,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -27105,12 +27105,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>28355</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>33859</t>
+          <t>34074</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -27120,12 +27120,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>27344</t>
+          <t>28097</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>58497</t>
+          <t>58404</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>64489</t>
+          <t>64506</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -27190,12 +27190,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -27464,7 +27464,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -27560,7 +27560,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -27575,7 +27575,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -27671,7 +27671,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -27686,7 +27686,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -27782,7 +27782,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -27797,7 +27797,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -27817,7 +27817,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -27832,7 +27832,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -27867,7 +27867,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -27893,7 +27893,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -27928,7 +27928,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -27943,7 +27943,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -27958,12 +27958,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -27999,12 +27999,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21466</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -28014,12 +28014,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -28034,12 +28034,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -28049,12 +28049,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -28069,12 +28069,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>36854</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -28084,12 +28084,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -28110,12 +28110,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>117981</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>130442</t>
+          <t>130659</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -28125,12 +28125,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -28145,12 +28145,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>124903</t>
+          <t>124365</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>136089</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -28160,12 +28160,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -28180,12 +28180,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>246136</t>
+          <t>246342</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>263924</t>
+          <t>263065</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -28195,12 +28195,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -30028,7 +30028,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3782</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -30043,7 +30043,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -30078,7 +30078,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -30098,7 +30098,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2309</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -30209,7 +30209,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -30224,7 +30224,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -30250,7 +30250,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -30265,7 +30265,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -30280,12 +30280,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -30295,12 +30295,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -30315,12 +30315,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -30330,12 +30330,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -30356,12 +30356,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -30371,12 +30371,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -30391,12 +30391,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9343</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -30406,12 +30406,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -30426,12 +30426,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -30441,12 +30441,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,33%</t>
         </is>
       </c>
     </row>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5571</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -32184,7 +32184,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -32199,7 +32199,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -32219,7 +32219,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>2879</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -32234,7 +32234,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -32260,7 +32260,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -32275,7 +32275,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -32345,7 +32345,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -32366,7 +32366,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -32381,7 +32381,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -32401,7 +32401,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -32416,7 +32416,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -32436,12 +32436,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20235</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>27466</t>
+          <t>27396</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -32451,12 +32451,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -33300,7 +33300,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2846</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -33315,7 +33315,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -33335,7 +33335,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -33350,7 +33350,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -33406,7 +33406,7 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -33421,7 +33421,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -33441,7 +33441,7 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
@@ -33456,7 +33456,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -34194,7 +34194,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -34209,7 +34209,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -34229,7 +34229,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -34411,7 +34411,7 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -34426,7 +34426,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
@@ -34461,7 +34461,7 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -34644,7 +34644,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -34659,7 +34659,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -34679,7 +34679,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>5084</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -34694,7 +34694,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -34942,7 +34942,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -34977,7 +34977,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -34992,7 +34992,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -35012,7 +35012,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -35027,7 +35027,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -35270,12 +35270,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -35285,12 +35285,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -35305,12 +35305,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>842</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -35320,12 +35320,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -35340,12 +35340,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>11332</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -35355,12 +35355,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>14982</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>21173</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -35396,12 +35396,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -35416,12 +35416,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -35431,12 +35431,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -35451,12 +35451,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>35974</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>45827</t>
+          <t>45938</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -35466,12 +35466,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -36280,7 +36280,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -36315,7 +36315,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -36345,12 +36345,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -36360,12 +36360,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -36386,7 +36386,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -36401,7 +36401,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -36456,12 +36456,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>26934</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>31287</t>
+          <t>31325</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -36471,12 +36471,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -36654,7 +36654,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -36689,7 +36689,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -36876,7 +36876,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>6162</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -36891,7 +36891,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -36911,7 +36911,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>6028</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -36952,7 +36952,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -36967,7 +36967,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -36987,7 +36987,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -37002,7 +37002,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -37022,7 +37022,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -37063,7 +37063,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -37078,7 +37078,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -37098,7 +37098,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -37113,7 +37113,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -37133,7 +37133,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -37204,12 +37204,12 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -37219,12 +37219,12 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -37239,12 +37239,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>533</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -37259,7 +37259,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -37280,12 +37280,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2821</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -37295,12 +37295,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -37315,12 +37315,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12974</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -37330,12 +37330,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -37350,12 +37350,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -37365,12 +37365,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -37391,12 +37391,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>96329</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -37406,12 +37406,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -37426,12 +37426,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>123962</t>
+          <t>123834</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -37441,12 +37441,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -37461,12 +37461,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>202958</t>
+          <t>203340</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>218419</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -37476,12 +37476,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
